--- a/study/risultati_test.xlsx
+++ b/study/risultati_test.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Riepilogo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Punteggi'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Punteggi'!$A$1:$Q$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -461,24 +461,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:Q97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -504,55 +506,65 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Età</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Sesso</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Storia</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Modalità</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Fonte modalità</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Posizione</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>N domande</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Corrette</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Sbagliate</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>In bianco</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Doppie/invalide</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Punteggio %</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Fascia MT</t>
         </is>
@@ -579,43 +591,51 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>anguille</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>10</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L2" t="n">
         <v>8</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>2</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>80</v>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -642,43 +662,51 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>orso</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>2</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>14</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>9</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>5</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>64.3</v>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -705,43 +733,51 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>delfino</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
         <v>14</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>11</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>3</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
       <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>78.59999999999999</v>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -768,43 +804,51 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>panda</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>2</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>14</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>13</v>
       </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>92.90000000000001</v>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>CCRD</t>
         </is>
@@ -831,43 +875,51 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>delfino</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
         <v>14</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>4</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>8</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>14.3</v>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>RIDI</t>
         </is>
@@ -894,43 +946,51 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>panda</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>14</v>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J7" t="n">
         <v>2</v>
       </c>
       <c r="K7" t="n">
+        <v>14</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
         <v>4</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>8</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>14.3</v>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>RIDI</t>
         </is>
@@ -957,43 +1017,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>10</v>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" t="n">
         <v>9</v>
       </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>90</v>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -1020,43 +1088,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="I9" t="n">
-        <v>10</v>
-      </c>
-      <c r="J9" t="n">
-        <v>10</v>
-      </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>100</v>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="Q9" s="3" t="inlineStr">
         <is>
           <t>CCRD</t>
         </is>
@@ -1083,43 +1159,51 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>10</v>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" t="n">
         <v>9</v>
       </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>90</v>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -1146,43 +1230,51 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="I11" t="n">
-        <v>10</v>
-      </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" t="n">
         <v>9</v>
       </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
         <v>90</v>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -1209,43 +1301,51 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>gatta</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
         <v>12</v>
       </c>
-      <c r="J12" t="n">
-        <v>10</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
+        <v>10</v>
+      </c>
+      <c r="M12" t="n">
         <v>2</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>83.3</v>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -1272,43 +1372,51 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>sbadiglio</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" t="n">
-        <v>10</v>
-      </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" t="n">
         <v>6</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>4</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>60</v>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -1335,43 +1443,51 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>delfino</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="n">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
         <v>14</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>11</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>3</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>78.59999999999999</v>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -1398,43 +1514,51 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>panda</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>14</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>6</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>8</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
       <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>42.9</v>
       </c>
-      <c r="O15" s="5" t="inlineStr">
+      <c r="Q15" s="5" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -1461,43 +1585,51 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" t="n">
+        <v>9</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>delfino</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
         <v>14</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>9</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>5</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>64.3</v>
       </c>
-      <c r="O16" s="5" t="inlineStr">
+      <c r="Q16" s="5" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -1524,43 +1656,51 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" t="n">
+        <v>9</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>panda</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>14</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>9</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>5</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
         <v>64.3</v>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -1587,43 +1727,51 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>10</v>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L18" t="n">
         <v>5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>3</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>2</v>
       </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
         <v>50</v>
       </c>
-      <c r="O18" s="5" t="inlineStr">
+      <c r="Q18" s="5" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -1650,43 +1798,51 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
-        <v>10</v>
-      </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L19" t="n">
         <v>9</v>
       </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
         <v>90</v>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -1713,43 +1869,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" t="n">
+        <v>9</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>10</v>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>10</v>
+      </c>
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>80</v>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -1776,43 +1940,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" t="n">
+        <v>9</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
         <v>2</v>
       </c>
-      <c r="I21" t="n">
-        <v>10</v>
-      </c>
-      <c r="J21" t="n">
-        <v>10</v>
-      </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>100</v>
       </c>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="Q21" s="3" t="inlineStr">
         <is>
           <t>CCRD</t>
         </is>
@@ -1839,43 +2011,51 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>10</v>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
         <v>100</v>
       </c>
-      <c r="O22" s="3" t="inlineStr">
+      <c r="Q22" s="3" t="inlineStr">
         <is>
           <t>CCRD</t>
         </is>
@@ -1902,43 +2082,51 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
         <v>2</v>
       </c>
-      <c r="I23" t="n">
-        <v>10</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
+        <v>10</v>
+      </c>
+      <c r="L23" t="n">
         <v>8</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>2</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
         <v>80</v>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -1965,43 +2153,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>10</v>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>10</v>
+      </c>
+      <c r="L24" t="n">
         <v>5</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>5</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
       <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
         <v>50</v>
       </c>
-      <c r="O24" s="5" t="inlineStr">
+      <c r="Q24" s="5" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -2028,43 +2224,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
         <v>2</v>
       </c>
-      <c r="I25" t="n">
-        <v>10</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
+        <v>10</v>
+      </c>
+      <c r="L25" t="n">
         <v>4</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>6</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
         <v>40</v>
       </c>
-      <c r="O25" s="4" t="inlineStr">
+      <c r="Q25" s="4" t="inlineStr">
         <is>
           <t>RIDI</t>
         </is>
@@ -2091,43 +2295,51 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>anguille</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>10</v>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>10</v>
+      </c>
+      <c r="L26" t="n">
         <v>9</v>
       </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>90</v>
       </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -2154,43 +2366,51 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>orso</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>14</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>7</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>7</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
       <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
         <v>50</v>
       </c>
-      <c r="O27" s="5" t="inlineStr">
+      <c r="Q27" s="5" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -2217,43 +2437,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" t="n">
+        <v>7</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" t="n">
-        <v>10</v>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>10</v>
+      </c>
+      <c r="L28" t="n">
         <v>8</v>
       </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
         <v>80</v>
       </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -2280,43 +2508,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" t="n">
+        <v>7</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
         <v>2</v>
       </c>
-      <c r="I29" t="n">
-        <v>10</v>
-      </c>
-      <c r="J29" t="n">
-        <v>10</v>
-      </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
         <v>100</v>
       </c>
-      <c r="O29" s="3" t="inlineStr">
+      <c r="Q29" s="3" t="inlineStr">
         <is>
           <t>CCRD</t>
         </is>
@@ -2343,43 +2579,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="n">
-        <v>10</v>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>10</v>
+      </c>
+      <c r="L30" t="n">
         <v>4</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>5</v>
       </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
       <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>40</v>
       </c>
-      <c r="O30" s="4" t="inlineStr">
+      <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>RIDI</t>
         </is>
@@ -2406,43 +2650,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="I31" t="n">
-        <v>10</v>
-      </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
+        <v>10</v>
+      </c>
+      <c r="L31" t="n">
         <v>9</v>
       </c>
-      <c r="K31" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
         <v>90</v>
       </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -2469,43 +2721,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" t="n">
+        <v>7</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" t="n">
-        <v>10</v>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
         <v>100</v>
       </c>
-      <c r="O32" s="3" t="inlineStr">
+      <c r="Q32" s="3" t="inlineStr">
         <is>
           <t>CCRD</t>
         </is>
@@ -2532,43 +2792,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
         <v>2</v>
       </c>
-      <c r="I33" t="n">
-        <v>10</v>
-      </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
+        <v>10</v>
+      </c>
+      <c r="L33" t="n">
         <v>7</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>3</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
       <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
         <v>70</v>
       </c>
-      <c r="O33" s="2" t="inlineStr">
+      <c r="Q33" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -2595,43 +2863,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" t="n">
-        <v>10</v>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>10</v>
+      </c>
+      <c r="L34" t="n">
         <v>8</v>
       </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
         <v>80</v>
       </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -2658,43 +2934,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="I35" t="n">
-        <v>10</v>
-      </c>
-      <c r="J35" t="n">
-        <v>10</v>
-      </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
         <v>100</v>
       </c>
-      <c r="O35" s="3" t="inlineStr">
+      <c r="Q35" s="3" t="inlineStr">
         <is>
           <t>CCRD</t>
         </is>
@@ -2721,43 +3005,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" t="n">
-        <v>10</v>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>10</v>
+      </c>
+      <c r="L36" t="n">
         <v>6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>4</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
       <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
         <v>60</v>
       </c>
-      <c r="O36" s="5" t="inlineStr">
+      <c r="Q36" s="5" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -2784,43 +3076,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" t="n">
+        <v>6</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
         <v>2</v>
       </c>
-      <c r="I37" t="n">
-        <v>10</v>
-      </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
+        <v>10</v>
+      </c>
+      <c r="L37" t="n">
         <v>9</v>
       </c>
-      <c r="K37" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
         <v>90</v>
       </c>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -2847,43 +3147,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" t="n">
+        <v>7</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" t="n">
-        <v>10</v>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>10</v>
+      </c>
+      <c r="L38" t="n">
         <v>9</v>
       </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
         <v>90</v>
       </c>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -2910,43 +3218,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" t="n">
+        <v>7</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
         <v>2</v>
       </c>
-      <c r="I39" t="n">
-        <v>10</v>
-      </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
+        <v>10</v>
+      </c>
+      <c r="L39" t="n">
         <v>6</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>2</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>2</v>
       </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
         <v>60</v>
       </c>
-      <c r="O39" s="5" t="inlineStr">
+      <c r="Q39" s="5" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -2973,43 +3289,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" t="n">
-        <v>10</v>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>10</v>
+      </c>
+      <c r="L40" t="n">
         <v>4</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>6</v>
       </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
       <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
         <v>40</v>
       </c>
-      <c r="O40" s="4" t="inlineStr">
+      <c r="Q40" s="4" t="inlineStr">
         <is>
           <t>RIDI</t>
         </is>
@@ -3036,43 +3360,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" t="n">
+        <v>6</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
         <v>2</v>
       </c>
-      <c r="I41" t="n">
-        <v>10</v>
-      </c>
-      <c r="J41" t="n">
-        <v>10</v>
-      </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
         <v>100</v>
       </c>
-      <c r="O41" s="3" t="inlineStr">
+      <c r="Q41" s="3" t="inlineStr">
         <is>
           <t>CCRD</t>
         </is>
@@ -3099,43 +3431,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" t="n">
-        <v>10</v>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>10</v>
+      </c>
+      <c r="L42" t="n">
         <v>6</v>
       </c>
-      <c r="K42" t="n">
+      <c r="M42" t="n">
         <v>3</v>
       </c>
-      <c r="L42" t="n">
-        <v>1</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
       <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
         <v>60</v>
       </c>
-      <c r="O42" s="5" t="inlineStr">
+      <c r="Q42" s="5" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -3162,43 +3502,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" t="n">
+        <v>7</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
         <v>2</v>
       </c>
-      <c r="I43" t="n">
-        <v>10</v>
-      </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
+        <v>10</v>
+      </c>
+      <c r="L43" t="n">
         <v>8</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
         <v>80</v>
       </c>
-      <c r="O43" s="2" t="inlineStr">
+      <c r="Q43" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -3225,43 +3573,51 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" t="n">
+        <v>7</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" t="n">
-        <v>10</v>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>10</v>
+      </c>
+      <c r="L44" t="n">
         <v>8</v>
       </c>
-      <c r="K44" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" t="n">
-        <v>1</v>
-      </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
         <v>80</v>
       </c>
-      <c r="O44" s="2" t="inlineStr">
+      <c r="Q44" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -3288,43 +3644,51 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" t="n">
+        <v>7</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
         <v>2</v>
       </c>
-      <c r="I45" t="n">
-        <v>10</v>
-      </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
+        <v>10</v>
+      </c>
+      <c r="L45" t="n">
         <v>7</v>
       </c>
-      <c r="K45" t="n">
+      <c r="M45" t="n">
         <v>3</v>
       </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
       <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
         <v>70</v>
       </c>
-      <c r="O45" s="2" t="inlineStr">
+      <c r="Q45" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -3351,43 +3715,51 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" t="n">
+        <v>8</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" t="n">
-        <v>10</v>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J46" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
         <v>100</v>
       </c>
-      <c r="O46" s="3" t="inlineStr">
+      <c r="Q46" s="3" t="inlineStr">
         <is>
           <t>CCRD</t>
         </is>
@@ -3414,43 +3786,51 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" t="n">
+        <v>8</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
         <v>2</v>
       </c>
-      <c r="I47" t="n">
-        <v>10</v>
-      </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
+        <v>10</v>
+      </c>
+      <c r="L47" t="n">
         <v>9</v>
       </c>
-      <c r="K47" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
         <v>90</v>
       </c>
-      <c r="O47" s="2" t="inlineStr">
+      <c r="Q47" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -3477,43 +3857,51 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" t="n">
+        <v>11</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>anguille</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>1</v>
-      </c>
-      <c r="I48" t="n">
-        <v>10</v>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>10</v>
+      </c>
+      <c r="L48" t="n">
         <v>8</v>
       </c>
-      <c r="K48" t="n">
+      <c r="M48" t="n">
         <v>2</v>
       </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
       <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
         <v>80</v>
       </c>
-      <c r="O48" s="2" t="inlineStr">
+      <c r="Q48" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -3540,43 +3928,51 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" t="n">
+        <v>11</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
         <is>
           <t>orso</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
         <v>2</v>
       </c>
-      <c r="I49" t="n">
+      <c r="K49" t="n">
         <v>14</v>
       </c>
-      <c r="J49" t="n">
+      <c r="L49" t="n">
         <v>8</v>
       </c>
-      <c r="K49" t="n">
+      <c r="M49" t="n">
         <v>6</v>
       </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
       <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
         <v>57.1</v>
       </c>
-      <c r="O49" s="5" t="inlineStr">
+      <c r="Q49" s="5" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -3603,43 +3999,51 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" t="n">
+        <v>7</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" t="n">
-        <v>10</v>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
         <v>100</v>
       </c>
-      <c r="O50" s="3" t="inlineStr">
+      <c r="Q50" s="3" t="inlineStr">
         <is>
           <t>CCRD</t>
         </is>
@@ -3666,43 +4070,51 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" t="n">
+        <v>7</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
         <v>2</v>
       </c>
-      <c r="I51" t="n">
-        <v>10</v>
-      </c>
-      <c r="J51" t="n">
-        <v>10</v>
-      </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
         <v>100</v>
       </c>
-      <c r="O51" s="3" t="inlineStr">
+      <c r="Q51" s="3" t="inlineStr">
         <is>
           <t>CCRD</t>
         </is>
@@ -3729,43 +4141,51 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" t="n">
+        <v>7</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" t="n">
-        <v>10</v>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>10</v>
+      </c>
+      <c r="L52" t="n">
         <v>7</v>
       </c>
-      <c r="K52" t="n">
+      <c r="M52" t="n">
         <v>3</v>
       </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
       <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
         <v>70</v>
       </c>
-      <c r="O52" s="5" t="inlineStr">
+      <c r="Q52" s="5" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -3792,43 +4212,51 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" t="n">
+        <v>7</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
         <v>2</v>
       </c>
-      <c r="I53" t="n">
-        <v>10</v>
-      </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
+        <v>10</v>
+      </c>
+      <c r="L53" t="n">
         <v>7</v>
       </c>
-      <c r="K53" t="n">
+      <c r="M53" t="n">
         <v>2</v>
       </c>
-      <c r="L53" t="n">
-        <v>1</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
       <c r="N53" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
         <v>70</v>
       </c>
-      <c r="O53" s="2" t="inlineStr">
+      <c r="Q53" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -3855,43 +4283,51 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" t="n">
+        <v>7</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>1</v>
-      </c>
-      <c r="I54" t="n">
-        <v>10</v>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>10</v>
+      </c>
+      <c r="L54" t="n">
         <v>8</v>
       </c>
-      <c r="K54" t="n">
-        <v>1</v>
-      </c>
-      <c r="L54" t="n">
-        <v>1</v>
-      </c>
       <c r="M54" t="n">
         <v>1</v>
       </c>
       <c r="N54" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" t="n">
         <v>80</v>
       </c>
-      <c r="O54" s="2" t="inlineStr">
+      <c r="Q54" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -3918,43 +4354,51 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" t="n">
+        <v>7</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
         <v>2</v>
       </c>
-      <c r="I55" t="n">
-        <v>10</v>
-      </c>
-      <c r="J55" t="n">
-        <v>10</v>
-      </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
       </c>
       <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
         <v>100</v>
       </c>
-      <c r="O55" s="3" t="inlineStr">
+      <c r="Q55" s="3" t="inlineStr">
         <is>
           <t>CCRD</t>
         </is>
@@ -3981,43 +4425,51 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" t="n">
+        <v>7</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>1</v>
-      </c>
-      <c r="I56" t="n">
-        <v>10</v>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>10</v>
+      </c>
+      <c r="L56" t="n">
         <v>8</v>
       </c>
-      <c r="K56" t="n">
+      <c r="M56" t="n">
         <v>2</v>
       </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
       <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
         <v>80</v>
       </c>
-      <c r="O56" s="2" t="inlineStr">
+      <c r="Q56" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -4044,43 +4496,51 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" t="n">
+        <v>7</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
         <v>2</v>
       </c>
-      <c r="I57" t="n">
-        <v>10</v>
-      </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
+        <v>10</v>
+      </c>
+      <c r="L57" t="n">
         <v>9</v>
       </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>1</v>
-      </c>
       <c r="M57" t="n">
         <v>0</v>
       </c>
       <c r="N57" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
         <v>90</v>
       </c>
-      <c r="O57" s="2" t="inlineStr">
+      <c r="Q57" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -4107,43 +4567,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" t="n">
+        <v>8</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
-        <v>1</v>
-      </c>
-      <c r="I58" t="n">
-        <v>10</v>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>10</v>
+      </c>
+      <c r="L58" t="n">
         <v>7</v>
       </c>
-      <c r="K58" t="n">
+      <c r="M58" t="n">
         <v>3</v>
       </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
       <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
         <v>70</v>
       </c>
-      <c r="O58" s="5" t="inlineStr">
+      <c r="Q58" s="5" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -4170,43 +4638,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" t="n">
+        <v>8</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
         <v>2</v>
       </c>
-      <c r="I59" t="n">
-        <v>10</v>
-      </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
+        <v>10</v>
+      </c>
+      <c r="L59" t="n">
         <v>8</v>
       </c>
-      <c r="K59" t="n">
+      <c r="M59" t="n">
         <v>2</v>
       </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
       <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
         <v>80</v>
       </c>
-      <c r="O59" s="2" t="inlineStr">
+      <c r="Q59" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -4233,43 +4709,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" t="n">
+        <v>7</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v>1</v>
-      </c>
-      <c r="I60" t="n">
-        <v>10</v>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>10</v>
+      </c>
+      <c r="L60" t="n">
         <v>5</v>
       </c>
-      <c r="K60" t="n">
+      <c r="M60" t="n">
         <v>4</v>
       </c>
-      <c r="L60" t="n">
-        <v>1</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
       <c r="N60" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
         <v>50</v>
       </c>
-      <c r="O60" s="5" t="inlineStr">
+      <c r="Q60" s="5" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -4296,43 +4780,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" t="n">
+        <v>7</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
         <v>2</v>
       </c>
-      <c r="I61" t="n">
-        <v>10</v>
-      </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
+        <v>10</v>
+      </c>
+      <c r="L61" t="n">
         <v>6</v>
       </c>
-      <c r="K61" t="n">
+      <c r="M61" t="n">
         <v>4</v>
       </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
       <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
         <v>60</v>
       </c>
-      <c r="O61" s="5" t="inlineStr">
+      <c r="Q61" s="5" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -4359,43 +4851,51 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E62" t="n">
+        <v>10</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
         <is>
           <t>delfino</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H62" t="n">
-        <v>1</v>
-      </c>
-      <c r="I62" t="n">
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
         <v>14</v>
       </c>
-      <c r="J62" t="n">
+      <c r="L62" t="n">
         <v>9</v>
       </c>
-      <c r="K62" t="n">
+      <c r="M62" t="n">
         <v>5</v>
       </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
       <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
         <v>64.3</v>
       </c>
-      <c r="O62" s="5" t="inlineStr">
+      <c r="Q62" s="5" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -4422,43 +4922,51 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" t="n">
+        <v>10</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
         <is>
           <t>panda</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H63" t="n">
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
         <v>2</v>
       </c>
-      <c r="I63" t="n">
+      <c r="K63" t="n">
         <v>14</v>
       </c>
-      <c r="J63" t="n">
+      <c r="L63" t="n">
         <v>8</v>
       </c>
-      <c r="K63" t="n">
+      <c r="M63" t="n">
         <v>6</v>
       </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
       <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
         <v>57.1</v>
       </c>
-      <c r="O63" s="2" t="inlineStr">
+      <c r="Q63" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -4485,43 +4993,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" t="n">
+        <v>7</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
-        <v>1</v>
-      </c>
-      <c r="I64" t="n">
-        <v>10</v>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>10</v>
+      </c>
+      <c r="L64" t="n">
         <v>9</v>
       </c>
-      <c r="K64" t="n">
-        <v>1</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
         <v>90</v>
       </c>
-      <c r="O64" s="2" t="inlineStr">
+      <c r="Q64" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -4548,43 +5064,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" t="n">
+        <v>7</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
         <v>2</v>
       </c>
-      <c r="I65" t="n">
-        <v>10</v>
-      </c>
-      <c r="J65" t="n">
+      <c r="K65" t="n">
+        <v>10</v>
+      </c>
+      <c r="L65" t="n">
         <v>9</v>
       </c>
-      <c r="K65" t="n">
-        <v>1</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
         <v>90</v>
       </c>
-      <c r="O65" s="2" t="inlineStr">
+      <c r="Q65" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -4611,43 +5135,51 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" t="n">
+        <v>9</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
         <is>
           <t>delfino</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H66" t="n">
-        <v>1</v>
-      </c>
-      <c r="I66" t="n">
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
         <v>14</v>
       </c>
-      <c r="J66" t="n">
+      <c r="L66" t="n">
         <v>8</v>
       </c>
-      <c r="K66" t="n">
+      <c r="M66" t="n">
         <v>6</v>
       </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
       <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
         <v>57.1</v>
       </c>
-      <c r="O66" s="5" t="inlineStr">
+      <c r="Q66" s="5" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -4674,43 +5206,51 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" t="n">
+        <v>9</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
         <is>
           <t>panda</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H67" t="n">
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
         <v>2</v>
       </c>
-      <c r="I67" t="n">
+      <c r="K67" t="n">
         <v>14</v>
       </c>
-      <c r="J67" t="n">
+      <c r="L67" t="n">
         <v>9</v>
       </c>
-      <c r="K67" t="n">
+      <c r="M67" t="n">
         <v>4</v>
       </c>
-      <c r="L67" t="n">
-        <v>1</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
       <c r="N67" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
         <v>64.3</v>
       </c>
-      <c r="O67" s="2" t="inlineStr">
+      <c r="Q67" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -4737,43 +5277,51 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" t="n">
+        <v>10</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
         <is>
           <t>delfino</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H68" t="n">
-        <v>1</v>
-      </c>
-      <c r="I68" t="n">
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="n">
         <v>14</v>
       </c>
-      <c r="J68" t="n">
+      <c r="L68" t="n">
         <v>7</v>
       </c>
-      <c r="K68" t="n">
+      <c r="M68" t="n">
         <v>7</v>
       </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="n">
-        <v>0</v>
-      </c>
       <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
         <v>50</v>
       </c>
-      <c r="O68" s="4" t="inlineStr">
+      <c r="Q68" s="4" t="inlineStr">
         <is>
           <t>RIDI</t>
         </is>
@@ -4800,43 +5348,51 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E69" t="n">
+        <v>10</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
         <is>
           <t>panda</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H69" t="n">
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
         <v>2</v>
       </c>
-      <c r="I69" t="n">
+      <c r="K69" t="n">
         <v>14</v>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>6</v>
       </c>
-      <c r="K69" t="n">
+      <c r="M69" t="n">
         <v>8</v>
       </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
       <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
         <v>42.9</v>
       </c>
-      <c r="O69" s="5" t="inlineStr">
+      <c r="Q69" s="5" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -4863,43 +5419,51 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E70" t="n">
+        <v>11</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
         <is>
           <t>anguille</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H70" t="n">
-        <v>1</v>
-      </c>
-      <c r="I70" t="n">
-        <v>10</v>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" t="n">
+        <v>10</v>
+      </c>
+      <c r="L70" t="n">
         <v>7</v>
       </c>
-      <c r="K70" t="n">
+      <c r="M70" t="n">
         <v>2</v>
       </c>
-      <c r="L70" t="n">
-        <v>1</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
       <c r="N70" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
         <v>70</v>
       </c>
-      <c r="O70" s="5" t="inlineStr">
+      <c r="Q70" s="5" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -4926,43 +5490,51 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E71" t="n">
+        <v>11</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
         <is>
           <t>orso</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H71" t="n">
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
         <v>2</v>
       </c>
-      <c r="I71" t="n">
+      <c r="K71" t="n">
         <v>14</v>
       </c>
-      <c r="J71" t="n">
+      <c r="L71" t="n">
         <v>5</v>
       </c>
-      <c r="K71" t="n">
+      <c r="M71" t="n">
         <v>9</v>
       </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
       <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
         <v>35.7</v>
       </c>
-      <c r="O71" s="4" t="inlineStr">
+      <c r="Q71" s="4" t="inlineStr">
         <is>
           <t>RIDI</t>
         </is>
@@ -4989,32 +5561,34 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E72" t="n">
+        <v>8</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H72" t="n">
-        <v>1</v>
-      </c>
-      <c r="I72" t="n">
-        <v>10</v>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L72" t="n">
         <v>5</v>
@@ -5023,9 +5597,15 @@
         <v>0</v>
       </c>
       <c r="N72" t="n">
+        <v>5</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
         <v>50</v>
       </c>
-      <c r="O72" s="5" t="inlineStr">
+      <c r="Q72" s="5" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -5052,43 +5632,51 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E73" t="n">
+        <v>8</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H73" t="n">
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
         <v>2</v>
       </c>
-      <c r="I73" t="n">
-        <v>10</v>
-      </c>
-      <c r="J73" t="n">
+      <c r="K73" t="n">
+        <v>10</v>
+      </c>
+      <c r="L73" t="n">
         <v>7</v>
       </c>
-      <c r="K73" t="n">
+      <c r="M73" t="n">
         <v>3</v>
       </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
       <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
         <v>70</v>
       </c>
-      <c r="O73" s="2" t="inlineStr">
+      <c r="Q73" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -5115,43 +5703,51 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E74" t="n">
+        <v>9</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>gatta</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>1</v>
-      </c>
-      <c r="I74" t="n">
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" t="n">
         <v>12</v>
       </c>
-      <c r="J74" t="n">
-        <v>10</v>
-      </c>
-      <c r="K74" t="n">
+      <c r="L74" t="n">
+        <v>10</v>
+      </c>
+      <c r="M74" t="n">
         <v>2</v>
       </c>
-      <c r="L74" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" t="n">
-        <v>0</v>
-      </c>
       <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
         <v>83.3</v>
       </c>
-      <c r="O74" s="2" t="inlineStr">
+      <c r="Q74" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -5178,43 +5774,51 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E75" t="n">
+        <v>9</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
         <is>
           <t>sbadiglio</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H75" t="n">
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
         <v>2</v>
       </c>
-      <c r="I75" t="n">
-        <v>10</v>
-      </c>
-      <c r="J75" t="n">
+      <c r="K75" t="n">
+        <v>10</v>
+      </c>
+      <c r="L75" t="n">
         <v>5</v>
       </c>
-      <c r="K75" t="n">
+      <c r="M75" t="n">
         <v>5</v>
       </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
       <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
         <v>50</v>
       </c>
-      <c r="O75" s="5" t="inlineStr">
+      <c r="Q75" s="5" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -5241,43 +5845,51 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E76" t="n">
+        <v>9</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>gatta</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H76" t="n">
-        <v>1</v>
-      </c>
-      <c r="I76" t="n">
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" t="n">
         <v>12</v>
       </c>
-      <c r="J76" t="n">
+      <c r="L76" t="n">
         <v>5</v>
       </c>
-      <c r="K76" t="n">
+      <c r="M76" t="n">
         <v>7</v>
       </c>
-      <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
       <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
         <v>41.7</v>
       </c>
-      <c r="O76" s="4" t="inlineStr">
+      <c r="Q76" s="4" t="inlineStr">
         <is>
           <t>RIDI</t>
         </is>
@@ -5304,43 +5916,51 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E77" t="n">
+        <v>9</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
         <is>
           <t>sbadiglio</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H77" t="n">
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
         <v>2</v>
       </c>
-      <c r="I77" t="n">
-        <v>10</v>
-      </c>
-      <c r="J77" t="n">
+      <c r="K77" t="n">
+        <v>10</v>
+      </c>
+      <c r="L77" t="n">
         <v>7</v>
       </c>
-      <c r="K77" t="n">
+      <c r="M77" t="n">
         <v>3</v>
       </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
       <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
         <v>70</v>
       </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="Q77" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -5367,43 +5987,51 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E78" t="n">
+        <v>8</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
         <is>
           <t>gatta</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H78" t="n">
-        <v>1</v>
-      </c>
-      <c r="I78" t="n">
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="n">
         <v>12</v>
       </c>
-      <c r="J78" t="n">
+      <c r="L78" t="n">
         <v>7</v>
       </c>
-      <c r="K78" t="n">
+      <c r="M78" t="n">
         <v>5</v>
       </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
       <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
         <v>58.3</v>
       </c>
-      <c r="O78" s="4" t="inlineStr">
+      <c r="Q78" s="4" t="inlineStr">
         <is>
           <t>RIDI</t>
         </is>
@@ -5430,43 +6058,51 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E79" t="n">
+        <v>8</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
         <is>
           <t>sbadiglio</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H79" t="n">
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
         <v>2</v>
       </c>
-      <c r="I79" t="n">
-        <v>10</v>
-      </c>
-      <c r="J79" t="n">
+      <c r="K79" t="n">
+        <v>10</v>
+      </c>
+      <c r="L79" t="n">
         <v>6</v>
       </c>
-      <c r="K79" t="n">
+      <c r="M79" t="n">
         <v>4</v>
       </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
       <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
         <v>60</v>
       </c>
-      <c r="O79" s="2" t="inlineStr">
+      <c r="Q79" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -5493,43 +6129,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E80" t="n">
+        <v>6</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H80" t="n">
-        <v>1</v>
-      </c>
-      <c r="I80" t="n">
-        <v>10</v>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J80" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" t="n">
+        <v>10</v>
+      </c>
+      <c r="L80" t="n">
         <v>4</v>
       </c>
-      <c r="K80" t="n">
+      <c r="M80" t="n">
         <v>5</v>
       </c>
-      <c r="L80" t="n">
-        <v>1</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
       <c r="N80" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
         <v>40</v>
       </c>
-      <c r="O80" s="4" t="inlineStr">
+      <c r="Q80" s="4" t="inlineStr">
         <is>
           <t>RIDI</t>
         </is>
@@ -5556,43 +6200,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E81" t="n">
+        <v>6</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H81" t="n">
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
         <v>2</v>
       </c>
-      <c r="I81" t="n">
-        <v>10</v>
-      </c>
-      <c r="J81" t="n">
+      <c r="K81" t="n">
+        <v>10</v>
+      </c>
+      <c r="L81" t="n">
         <v>9</v>
       </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>1</v>
-      </c>
       <c r="M81" t="n">
         <v>0</v>
       </c>
       <c r="N81" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
         <v>90</v>
       </c>
-      <c r="O81" s="2" t="inlineStr">
+      <c r="Q81" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -5619,43 +6271,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E82" t="n">
+        <v>6</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H82" t="n">
-        <v>1</v>
-      </c>
-      <c r="I82" t="n">
-        <v>10</v>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J82" t="n">
         <v>1</v>
       </c>
       <c r="K82" t="n">
+        <v>10</v>
+      </c>
+      <c r="L82" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" t="n">
         <v>5</v>
       </c>
-      <c r="L82" t="n">
+      <c r="N82" t="n">
         <v>4</v>
       </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
-        <v>10</v>
-      </c>
-      <c r="O82" s="4" t="inlineStr">
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q82" s="4" t="inlineStr">
         <is>
           <t>RIDI</t>
         </is>
@@ -5682,43 +6342,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E83" t="n">
+        <v>6</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H83" t="n">
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
         <v>2</v>
       </c>
-      <c r="I83" t="n">
-        <v>10</v>
-      </c>
-      <c r="J83" t="n">
+      <c r="K83" t="n">
+        <v>10</v>
+      </c>
+      <c r="L83" t="n">
         <v>3</v>
       </c>
-      <c r="K83" t="n">
+      <c r="M83" t="n">
         <v>7</v>
       </c>
-      <c r="L83" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
       <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
         <v>30</v>
       </c>
-      <c r="O83" s="4" t="inlineStr">
+      <c r="Q83" s="4" t="inlineStr">
         <is>
           <t>RIDI</t>
         </is>
@@ -5745,43 +6413,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E84" t="n">
+        <v>6</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H84" t="n">
-        <v>1</v>
-      </c>
-      <c r="I84" t="n">
-        <v>10</v>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
+        <v>10</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
         <v>2</v>
       </c>
-      <c r="L84" t="n">
+      <c r="N84" t="n">
         <v>8</v>
       </c>
-      <c r="M84" t="n">
-        <v>1</v>
-      </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" s="4" t="inlineStr">
+      <c r="O84" t="n">
+        <v>1</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="4" t="inlineStr">
         <is>
           <t>RIDI</t>
         </is>
@@ -5808,43 +6484,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E85" t="n">
+        <v>6</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H85" t="n">
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
         <v>2</v>
       </c>
-      <c r="I85" t="n">
-        <v>10</v>
-      </c>
-      <c r="J85" t="n">
+      <c r="K85" t="n">
+        <v>10</v>
+      </c>
+      <c r="L85" t="n">
         <v>4</v>
       </c>
-      <c r="K85" t="n">
+      <c r="M85" t="n">
         <v>4</v>
       </c>
-      <c r="L85" t="n">
+      <c r="N85" t="n">
         <v>2</v>
       </c>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="n">
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
         <v>40</v>
       </c>
-      <c r="O85" s="4" t="inlineStr">
+      <c r="Q85" s="4" t="inlineStr">
         <is>
           <t>RIDI</t>
         </is>
@@ -5871,43 +6555,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E86" t="n">
+        <v>7</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H86" t="n">
-        <v>1</v>
-      </c>
-      <c r="I86" t="n">
-        <v>10</v>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J86" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" t="n">
+        <v>10</v>
+      </c>
+      <c r="L86" t="n">
         <v>7</v>
       </c>
-      <c r="K86" t="n">
+      <c r="M86" t="n">
         <v>3</v>
       </c>
-      <c r="L86" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
       <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
         <v>70</v>
       </c>
-      <c r="O86" s="5" t="inlineStr">
+      <c r="Q86" s="5" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -5934,43 +6626,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E87" t="n">
+        <v>7</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H87" t="n">
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
         <v>2</v>
       </c>
-      <c r="I87" t="n">
-        <v>10</v>
-      </c>
-      <c r="J87" t="n">
-        <v>10</v>
-      </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
       </c>
       <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
         <v>100</v>
       </c>
-      <c r="O87" s="3" t="inlineStr">
+      <c r="Q87" s="3" t="inlineStr">
         <is>
           <t>CCRD</t>
         </is>
@@ -5997,43 +6697,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E88" t="n">
+        <v>7</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H88" t="n">
-        <v>1</v>
-      </c>
-      <c r="I88" t="n">
-        <v>10</v>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J88" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
       </c>
       <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
         <v>100</v>
       </c>
-      <c r="O88" s="3" t="inlineStr">
+      <c r="Q88" s="3" t="inlineStr">
         <is>
           <t>CCRD</t>
         </is>
@@ -6060,43 +6768,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E89" t="n">
+        <v>7</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H89" t="n">
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
         <v>2</v>
       </c>
-      <c r="I89" t="n">
-        <v>10</v>
-      </c>
-      <c r="J89" t="n">
+      <c r="K89" t="n">
+        <v>10</v>
+      </c>
+      <c r="L89" t="n">
         <v>9</v>
       </c>
-      <c r="K89" t="n">
-        <v>1</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0</v>
-      </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
         <v>90</v>
       </c>
-      <c r="O89" s="2" t="inlineStr">
+      <c r="Q89" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -6123,43 +6839,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E90" t="n">
+        <v>7</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H90" t="n">
-        <v>1</v>
-      </c>
-      <c r="I90" t="n">
-        <v>10</v>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J90" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" t="n">
+        <v>10</v>
+      </c>
+      <c r="L90" t="n">
         <v>3</v>
       </c>
-      <c r="K90" t="n">
+      <c r="M90" t="n">
         <v>7</v>
       </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
       <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
         <v>30</v>
       </c>
-      <c r="O90" s="4" t="inlineStr">
+      <c r="Q90" s="4" t="inlineStr">
         <is>
           <t>RIDI</t>
         </is>
@@ -6186,43 +6910,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E91" t="n">
+        <v>7</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H91" t="n">
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
         <v>2</v>
       </c>
-      <c r="I91" t="n">
-        <v>10</v>
-      </c>
-      <c r="J91" t="n">
+      <c r="K91" t="n">
+        <v>10</v>
+      </c>
+      <c r="L91" t="n">
         <v>3</v>
       </c>
-      <c r="K91" t="n">
+      <c r="M91" t="n">
         <v>6</v>
       </c>
-      <c r="L91" t="n">
-        <v>1</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
       <c r="N91" t="n">
+        <v>1</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
         <v>30</v>
       </c>
-      <c r="O91" s="4" t="inlineStr">
+      <c r="Q91" s="4" t="inlineStr">
         <is>
           <t>RIDI</t>
         </is>
@@ -6249,43 +6981,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E92" t="n">
+        <v>7</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H92" t="n">
-        <v>1</v>
-      </c>
-      <c r="I92" t="n">
-        <v>10</v>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J92" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" t="n">
+        <v>10</v>
+      </c>
+      <c r="L92" t="n">
         <v>6</v>
       </c>
-      <c r="K92" t="n">
+      <c r="M92" t="n">
         <v>4</v>
       </c>
-      <c r="L92" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
       <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
         <v>60</v>
       </c>
-      <c r="O92" s="5" t="inlineStr">
+      <c r="Q92" s="5" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -6312,43 +7052,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E93" t="n">
+        <v>7</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H93" t="n">
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
         <v>2</v>
       </c>
-      <c r="I93" t="n">
-        <v>10</v>
-      </c>
-      <c r="J93" t="n">
+      <c r="K93" t="n">
+        <v>10</v>
+      </c>
+      <c r="L93" t="n">
         <v>8</v>
       </c>
-      <c r="K93" t="n">
+      <c r="M93" t="n">
         <v>2</v>
       </c>
-      <c r="L93" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" t="n">
-        <v>0</v>
-      </c>
       <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
         <v>80</v>
       </c>
-      <c r="O93" s="2" t="inlineStr">
+      <c r="Q93" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -6375,43 +7123,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E94" t="n">
+        <v>6</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>volpe e boscaiolo</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H94" t="n">
-        <v>1</v>
-      </c>
-      <c r="I94" t="n">
-        <v>10</v>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
       </c>
       <c r="J94" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" t="n">
+        <v>10</v>
+      </c>
+      <c r="L94" t="n">
         <v>9</v>
       </c>
-      <c r="K94" t="n">
-        <v>1</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0</v>
-      </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
         <v>90</v>
       </c>
-      <c r="O94" s="2" t="inlineStr">
+      <c r="Q94" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -6438,43 +7194,51 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E95" t="n">
+        <v>6</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>tappeto</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H95" t="n">
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
         <v>2</v>
       </c>
-      <c r="I95" t="n">
-        <v>10</v>
-      </c>
-      <c r="J95" t="n">
+      <c r="K95" t="n">
+        <v>10</v>
+      </c>
+      <c r="L95" t="n">
         <v>9</v>
       </c>
-      <c r="K95" t="n">
-        <v>1</v>
-      </c>
-      <c r="L95" t="n">
-        <v>0</v>
-      </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
         <v>90</v>
       </c>
-      <c r="O95" s="2" t="inlineStr">
+      <c r="Q95" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
@@ -6501,43 +7265,51 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E96" t="n">
+        <v>8</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
         <is>
           <t>gatta</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H96" t="n">
-        <v>1</v>
-      </c>
-      <c r="I96" t="n">
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>1</v>
+      </c>
+      <c r="K96" t="n">
         <v>12</v>
       </c>
-      <c r="J96" t="n">
+      <c r="L96" t="n">
         <v>8</v>
       </c>
-      <c r="K96" t="n">
+      <c r="M96" t="n">
         <v>4</v>
       </c>
-      <c r="L96" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0</v>
-      </c>
       <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
         <v>66.7</v>
       </c>
-      <c r="O96" s="5" t="inlineStr">
+      <c r="Q96" s="5" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
@@ -6564,50 +7336,58 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E97" t="n">
+        <v>8</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
         <is>
           <t>sbadiglio</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>gaze</t>
-        </is>
-      </c>
-      <c r="H97" t="n">
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>gaze</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
         <v>2</v>
       </c>
-      <c r="I97" t="n">
-        <v>10</v>
-      </c>
-      <c r="J97" t="n">
+      <c r="K97" t="n">
+        <v>10</v>
+      </c>
+      <c r="L97" t="n">
         <v>6</v>
       </c>
-      <c r="K97" t="n">
+      <c r="M97" t="n">
         <v>4</v>
       </c>
-      <c r="L97" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" t="n">
-        <v>0</v>
-      </c>
       <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
         <v>60</v>
       </c>
-      <c r="O97" s="2" t="inlineStr">
+      <c r="Q97" s="2" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:Q97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6920,7 +7700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -7442,14 +8222,171 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Nota metodologica: prove MT applicate per tutti all'uscita (fine anno); somministrazione</t>
-        </is>
-      </c>
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>DEMOGRAFIA (soggetti validi)</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
+        <is>
+          <t>Gruppo</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>età media</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>età min-max</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>27</v>
+      </c>
+      <c r="C38" t="n">
+        <v>13</v>
+      </c>
+      <c r="D38" t="n">
+        <v>14</v>
+      </c>
+      <c r="E38" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>6-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>21</v>
+      </c>
+      <c r="C39" t="n">
+        <v>12</v>
+      </c>
+      <c r="D39" t="n">
+        <v>9</v>
+      </c>
+      <c r="E39" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>6-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>PUNTEGGIO PER SESSO</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="7" t="n"/>
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Sesso</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>media %</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>25</v>
+      </c>
+      <c r="C43" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="D43" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>23</v>
+      </c>
+      <c r="C44" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="D44" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Nota metodologica: prove MT applicate per tutti all'uscita (fine anno); somministrazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>non standard (ascolto + caption, non lettura), fasce da intendersi come riferimento descrittivo.</t>
         </is>

--- a/study/risultati_test.xlsx
+++ b/study/risultati_test.xlsx
@@ -1402,10 +1402,10 @@
         <v>10</v>
       </c>
       <c r="L13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1414,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
@@ -5804,10 +5804,10 @@
         <v>10</v>
       </c>
       <c r="L75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
@@ -5816,11 +5816,11 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q75" s="5" t="inlineStr">
-        <is>
-          <t>RAD</t>
+        <v>60</v>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>PSD</t>
         </is>
       </c>
     </row>
@@ -5946,10 +5946,10 @@
         <v>10</v>
       </c>
       <c r="L77" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N77" t="n">
         <v>0</v>
@@ -5958,7 +5958,7 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="Q77" s="2" t="inlineStr">
         <is>
@@ -6088,10 +6088,10 @@
         <v>10</v>
       </c>
       <c r="L79" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N79" t="n">
         <v>0</v>
@@ -6100,7 +6100,7 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="Q79" s="2" t="inlineStr">
         <is>
@@ -7366,10 +7366,10 @@
         <v>10</v>
       </c>
       <c r="L97" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M97" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N97" t="n">
         <v>0</v>
@@ -7378,7 +7378,7 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="Q97" s="2" t="inlineStr">
         <is>
@@ -7749,10 +7749,10 @@
         <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>69.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="4">
@@ -7765,10 +7765,10 @@
         <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>70.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="D4" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="6">
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="9">
@@ -7808,7 +7808,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.28</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="10">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21 / 19 / 8</t>
+          <t>22 / 18 / 8</t>
         </is>
       </c>
     </row>
@@ -7965,13 +7965,13 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D19" t="n">
         <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>60</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="20">
@@ -8098,13 +8098,13 @@
         <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D27" t="n">
         <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>64.7</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="28">
@@ -8212,10 +8212,10 @@
         <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E34" t="n">
         <v>7</v>
@@ -8356,10 +8356,10 @@
         <v>25</v>
       </c>
       <c r="C43" t="n">
-        <v>74.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="D43" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="44">
@@ -8372,10 +8372,10 @@
         <v>23</v>
       </c>
       <c r="C44" t="n">
-        <v>64.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="46">

--- a/study/risultati_test.xlsx
+++ b/study/risultati_test.xlsx
@@ -692,10 +692,10 @@
         <v>14</v>
       </c>
       <c r="L3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>64.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
@@ -2396,10 +2396,10 @@
         <v>14</v>
       </c>
       <c r="L27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
@@ -3958,10 +3958,10 @@
         <v>14</v>
       </c>
       <c r="L49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -3970,11 +3970,11 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="Q49" s="5" t="inlineStr">
-        <is>
-          <t>RAD</t>
+        <v>64.3</v>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>PSD</t>
         </is>
       </c>
     </row>
@@ -7749,10 +7749,10 @@
         <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>69.59999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>25.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -7765,10 +7765,10 @@
         <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>71.2</v>
+        <v>71.3</v>
       </c>
       <c r="D4" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="6">
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="9">
@@ -7808,7 +7808,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="10">
@@ -7927,13 +7927,13 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>57.1</v>
+        <v>64.2</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>46.4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -8136,13 +8136,13 @@
         <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>66.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D29" t="n">
         <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>65.7</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="31">
@@ -8212,10 +8212,10 @@
         <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E34" t="n">
         <v>7</v>
@@ -8356,10 +8356,10 @@
         <v>25</v>
       </c>
       <c r="C43" t="n">
-        <v>74.5</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="44">
